--- a/data/output/bfmaster.xlsx
+++ b/data/output/bfmaster.xlsx
@@ -36,48 +36,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gholdengo A+SB/FB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>steel/ghost</t>
+          <t>steel/psychic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>psychic/flying</t>
+          <t>ghost/poison</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Yveltal SkP+DP/ObW 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dark/flying</t>
+          <t>water/none</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>water/none</t>
+          <t>fairy/flying</t>
         </is>
       </c>
     </row>
@@ -96,12 +96,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fairy/none</t>
+          <t>dragon/flying</t>
         </is>
       </c>
     </row>
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -201,7 +201,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>191.3984748726641</v>
+        <v>166.55672080256633</v>
       </c>
     </row>
     <row r="10">
@@ -211,7 +211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>152.3015873015873</v>
+        <v>78.3219814241486</v>
       </c>
     </row>
     <row r="11">
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>208.14421800346267</v>
+        <v>160.65271462487303</v>
       </c>
     </row>
     <row r="12">
@@ -231,7 +231,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>768.6078431372549</v>
+        <v>823.2745098039217</v>
       </c>
     </row>
     <row r="13">
@@ -241,7 +241,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.803921568627451</v>
+        <v>0.8627450980392157</v>
       </c>
     </row>
     <row r="15">
@@ -261,7 +261,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>708.3137254901961</v>
+        <v>758.5686274509804</v>
       </c>
     </row>
     <row r="17">
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -291,7 +291,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.0196078431372549</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>87.6</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="28">
@@ -391,7 +391,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>68.23333333333333</v>
+        <v>63.757746478873244</v>
       </c>
     </row>
     <row r="29">
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>54.4</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="30">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>71.58333333333333</v>
+        <v>78.11666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.058823529411764705</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>630.9861111111112</v>
+        <v>715.5294117647059</v>
       </c>
     </row>
   </sheetData>
@@ -522,16 +522,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.916667</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -596,7 +596,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Gholdengo A+SB/FB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
     </row>
@@ -616,22 +616,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>ABA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -646,17 +646,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Gholdengo A+SB/FB 15/15/15</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
         </is>
       </c>
     </row>
@@ -696,17 +696,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Yveltal SkP+DP/ObW 15/15/15</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
+          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gholdengo A+SB/FB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yveltal SkP+DP/ObW 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
     </row>
@@ -796,17 +796,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Yveltal SkP+DP/ObW 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gholdengo A+SB/FB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lugia DT+A/Fl 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zacian (Hero) Sn+WC/CC 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yveltal SkP+DP/ObW 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -867,36 +867,180 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Florges FW+TBl/CW 15/15/15</t>
+          <t>Swampert (Mega) MS+HC/Eq 15/15/15</t>
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-shield only Gholdengo A+SB/FB 15/15/15 | 1-shield no cover</t>
+          <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Ampharos (Mega) VS+TBl/BrS 15/15/15</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Dialga (Origin) DB+ROT/IH 15/15/15</t>
         </is>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0-shield only Tyranitar DB+BrS/SE 15/15/15 | 1-shield only Zacian (Hero) Sn+WC/CC 15/15/15</t>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lugia (Shadow) DT+A/Fl 15/15/15</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Reshiram DB+FuF/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dialga DB+IH/DM 15/15/15</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Zamazenta (Crowned Shield) IF+CC/BB 15/15/15</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gyarados (Shadow) DB+AT/Tw 15/15/15</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Gholdengo A+SB/DG 15/15/15</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>

--- a/data/output/bfmaster.xlsx
+++ b/data/output/bfmaster.xlsx
@@ -36,19 +36,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>steel/psychic</t>
+          <t>water/none</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -60,48 +60,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
+          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>water/none</t>
+          <t>fairy/flying</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fairy/flying</t>
+          <t>dragon/flying</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rock/dark</t>
+          <t>steel/psychic</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dragon/flying</t>
+          <t>rock/dark</t>
         </is>
       </c>
     </row>
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>377.4611398963731</v>
+        <v>190.96</v>
       </c>
     </row>
     <row r="9">
@@ -201,7 +201,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>166.55672080256633</v>
+        <v>162.7819947772733</v>
       </c>
     </row>
     <row r="10">
@@ -211,7 +211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>78.3219814241486</v>
+        <v>88.3810888252149</v>
       </c>
     </row>
     <row r="11">
@@ -231,7 +231,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>823.2745098039217</v>
+        <v>822.1111111111111</v>
       </c>
     </row>
     <row r="13">
@@ -241,7 +241,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.8627450980392157</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="15">
@@ -261,7 +261,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>758.5686274509804</v>
+        <v>757.8253968253969</v>
       </c>
     </row>
     <row r="17">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>100.0</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="28">
@@ -391,7 +391,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>63.757746478873244</v>
+        <v>76.7625</v>
       </c>
     </row>
     <row r="29">
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>28.9</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="30">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.0</v>
+        <v>0.015873015873015872</v>
       </c>
     </row>
     <row r="34">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>715.5294117647059</v>
+        <v>686.8472222222224</v>
       </c>
     </row>
   </sheetData>
@@ -505,7 +505,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -522,7 +522,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -616,17 +616,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABA</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gengar (Mega) SC+ShP/SlB 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
     </row>
@@ -746,17 +746,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+DG/AuS 15/15/15</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -796,17 +796,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Dragonite DB+TP/SP 15/15/15</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+DG/AuS 15/15/15</t>
-        </is>
-      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Metagross SC+MM/Eq 15/15/15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>
@@ -867,180 +867,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swampert (Mega) MS+HC/Eq 15/15/15</t>
+          <t>Scizor (Mega) BP+TBl/NS 15/15/15</t>
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ampharos (Mega) VS+TBl/BrS 15/15/15</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dialga (Origin) DB+ROT/IH 15/15/15</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Lugia (Shadow) DT+A/Fl 15/15/15</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Reshiram DB+FuF/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dialga DB+IH/DM 15/15/15</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Zamazenta (Crowned Shield) IF+CC/BB 15/15/15</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Gyarados (Shadow) DB+AT/Tw 15/15/15</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gholdengo A+SB/DG 15/15/15</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>1-shield only Kyogre W+Av/OP 15/15/15</t>
         </is>
       </c>
     </row>

--- a/data/output/bfmaster.xlsx
+++ b/data/output/bfmaster.xlsx
@@ -7,6 +7,10 @@
     <sheet name="Coverage" sheetId="3" r:id="rId3"/>
     <sheet name="Safe Cores" sheetId="4" r:id="rId4"/>
     <sheet name="Threats" sheetId="5" r:id="rId5"/>
+    <sheet name="Lineups" sheetId="6" r:id="rId6"/>
+    <sheet name="Lineup Resources" sheetId="7" r:id="rId7"/>
+    <sheet name="Bench Utility" sheetId="8" r:id="rId8"/>
+    <sheet name="Bench Warnings" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -36,72 +40,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>water/none</t>
+          <t>rock/dark</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ghost/poison</t>
+          <t>fire/flying</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
+          <t>Groudon DT+FiP/PrB 15/15/15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fairy/flying</t>
+          <t>ground/none</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
+          <t>Zekrom DB+O/FuB 15/15/15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>dragon/flying</t>
+          <t>dragon/electric</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>steel/psychic</t>
+          <t>fairy/flying</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+          <t>Goodra DB+AT/TP 15/15/15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rock/dark</t>
+          <t>dragon/none</t>
         </is>
       </c>
     </row>
@@ -137,37 +141,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>battle_frontier_max_five_point_members</t>
+          <t>battle_frontier_free_low_point_usage_rate</t>
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>battle_frontier_max_mega_members</t>
+          <t>battle_frontier_high_point_usage_rate</t>
         </is>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>battle_frontier_max_points</t>
+          <t>battle_frontier_max_five_point_members</t>
         </is>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>battle_frontier_mega_members</t>
+          <t>battle_frontier_max_mega_members</t>
         </is>
       </c>
       <c r="B6">
@@ -177,7 +181,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>battle_frontier_points_used</t>
+          <t>battle_frontier_max_points</t>
         </is>
       </c>
       <c r="B7">
@@ -187,283 +191,373 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bulk_pool_max</t>
+          <t>battle_frontier_mega_members</t>
         </is>
       </c>
       <c r="B8">
-        <v>190.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bulk_pool_mean</t>
+          <t>battle_frontier_points_used</t>
         </is>
       </c>
       <c r="B9">
-        <v>162.7819947772733</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bulk_pool_min</t>
+          <t>bulk_pool_max</t>
         </is>
       </c>
       <c r="B10">
-        <v>88.3810888252149</v>
+        <v>377.4611398963731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bulk_score</t>
+          <t>bulk_pool_mean</t>
         </is>
       </c>
       <c r="B11">
-        <v>160.65271462487303</v>
+        <v>166.55672080256633</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>consistency_score</t>
+          <t>bulk_pool_min</t>
         </is>
       </c>
       <c r="B12">
-        <v>822.1111111111111</v>
+        <v>78.3219814241486</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dominate_count</t>
+          <t>bulk_score</t>
         </is>
       </c>
       <c r="B13">
-        <v>54</v>
+        <v>176.37184573213008</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dominate_rate</t>
+          <t>consistency_score</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.8571428571428571</v>
+        <v>820.3541666666666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>full_col_coverage</t>
+          <t>dominate_count</t>
         </is>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mean_best_score</t>
+          <t>dominate_rate</t>
         </is>
       </c>
       <c r="B16">
-        <v>757.8253968253969</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>no_cover_pairs</t>
+          <t>full_col_coverage</t>
         </is>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>no_cover_rate</t>
+          <t>legacy_full_roster_dominate_count</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>overwhelming_count</t>
+          <t>legacy_full_roster_mean_best_score</t>
         </is>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>753.6875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>overwhelming_rate</t>
+          <t>legacy_full_roster_overwhelming_count</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pair_coverage</t>
+          <t>lineup_best_score</t>
         </is>
       </c>
       <c r="B21">
-        <v>63</v>
+        <v>732.9583333333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>redundant_coverage_2plus</t>
+          <t>lineup_objective_score</t>
         </is>
       </c>
       <c r="B22">
-        <v>62</v>
+        <v>634.1865277777779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>redundant_coverage_3plus</t>
+          <t>lineup_top_n_mean_score</t>
         </is>
       </c>
       <c r="B23">
-        <v>48</v>
+        <v>723.3881944444445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>safe_member_floor</t>
+          <t>lineup_viable_count</t>
         </is>
       </c>
       <c r="B24">
-        <v>90.0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>safe_member_target</t>
+          <t>mean_best_score</t>
         </is>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>753.6875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>safety_floor_target</t>
+          <t>no_cover_pairs</t>
         </is>
       </c>
       <c r="B26">
-        <v>78.0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>safety_pool_max</t>
+          <t>no_cover_rate</t>
         </is>
       </c>
       <c r="B27">
-        <v>93.3</v>
+        <v>0.020833333333333332</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>safety_pool_mean</t>
+          <t>overwhelming_count</t>
         </is>
       </c>
       <c r="B28">
-        <v>76.7625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>safety_pool_min</t>
+          <t>overwhelming_rate</t>
         </is>
       </c>
       <c r="B29">
-        <v>69.7</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>safety_priority</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>pair_coverage</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>safety_score</t>
+          <t>redundant_coverage_2plus</t>
         </is>
       </c>
       <c r="B31">
-        <v>78.11666666666667</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>single_cover_pairs</t>
+          <t>redundant_coverage_3plus</t>
         </is>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>single_cover_rate</t>
+          <t>safe_member_floor</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.015873015873015872</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>total_pairs</t>
+          <t>safe_member_target</t>
         </is>
       </c>
       <c r="B34">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>safety_floor_target</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>78.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>safety_pool_max</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>safety_pool_mean</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>63.757746478873244</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>safety_pool_min</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>safety_priority</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>safety_score</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>78.26666666666667</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>single_cover_pairs</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>single_cover_rate</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.08333333333333333</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>total_pairs</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>weighted_worst_best_score</t>
         </is>
       </c>
-      <c r="B35">
-        <v>686.8472222222224</v>
+      <c r="B44">
+        <v>685.4565217391304</v>
       </c>
     </row>
   </sheetData>
@@ -505,16 +599,16 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>1.0</v>
+        <v>0.978261</v>
       </c>
     </row>
     <row r="3">
@@ -522,16 +616,16 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>1.0</v>
+        <v>0.978261</v>
       </c>
     </row>
     <row r="4">
@@ -539,16 +633,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1.0</v>
+        <v>0.978261</v>
       </c>
     </row>
   </sheetData>
@@ -585,256 +679,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Gengar (Mega) SC+SB/ShP 15/15/15</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Dragonite DB+TP/SP 15/15/15</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Kyogre W+Av/OP 15/15/15</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Metagross SC+MM/Eq 15/15/15</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Togekiss Pk+Ft/AuS 15/15/15</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Tyranitar DB+BrS/SE 15/15/15</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -867,18 +711,1480 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scizor (Mega) BP+TBl/NS 15/15/15</t>
+          <t>Swampert (Mega) MS+HC/Eq 15/15/15</t>
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1-shield only Kyogre W+Av/OP 15/15/15</t>
+          <t>0-shield no cover | 1-shield no cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Florges FW+CW/M 15/15/15</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2-shield no cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Xerneas Geo+CC/M 15/15/15</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0-shield only Charizard (Mega Y) DB+BB/AC 15/15/15 | 1-shield only Charizard (Mega Y) DB+BB/AC 15/15/15 | 2-shield only Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gardevoir (Mega) Ch+TAx/SB 15/15/15</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0-shield only Charizard (Mega Y) DB+BB/AC 15/15/15 | 1-shield only Charizard (Mega Y) DB+BB/AC 15/15/15 | 2-shield only Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aggron (Mega) DT+RT/MeB 15/15/15</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1-shield only Groudon DT+FiP/PrB 15/15/15 | 2-shield only Groudon DT+FiP/PrB 15/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Scizor (Mega) FC+TBl/IH 15/15/15</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1-shield only Charizard (Mega Y) DB+BB/AC 15/15/15 | 2-shield only Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Zekrom DB+FuB/O 15/15/15</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0-shield only Groudon DT+FiP/PrB 15/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kyurem (Black) DT+FSh/FuB 15/15/15</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0-shield only Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Back 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Team Shape</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lineup Score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mean Score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Battle Frontier Points Used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>732.9583333333334</v>
+      </c>
+      <c r="G2">
+        <v>732.9583333333334</v>
+      </c>
+      <c r="H2">
+        <v>127</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>729.6041666666666</v>
+      </c>
+      <c r="G3">
+        <v>729.6041666666666</v>
+      </c>
+      <c r="H3">
+        <v>125</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>727.75</v>
+      </c>
+      <c r="G4">
+        <v>727.75</v>
+      </c>
+      <c r="H4">
+        <v>122</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Zekrom DB+O/FuB 15/15/15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>721.8472222222223</v>
+      </c>
+      <c r="G5">
+        <v>721.8472222222223</v>
+      </c>
+      <c r="H5">
+        <v>121</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zekrom DB+O/FuB 15/15/15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>721.2777777777778</v>
+      </c>
+      <c r="G6">
+        <v>721.2777777777778</v>
+      </c>
+      <c r="H6">
+        <v>121</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Groudon DT+FiP/PrB 15/15/15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>720.5277777777778</v>
+      </c>
+      <c r="G7">
+        <v>720.5277777777778</v>
+      </c>
+      <c r="H7">
+        <v>120</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Groudon DT+FiP/PrB 15/15/15</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>720.4722222222222</v>
+      </c>
+      <c r="G8">
+        <v>720.4722222222222</v>
+      </c>
+      <c r="H8">
+        <v>118</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Groudon DT+FiP/PrB 15/15/15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>720.1527777777778</v>
+      </c>
+      <c r="G9">
+        <v>720.1527777777778</v>
+      </c>
+      <c r="H9">
+        <v>117</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Togekiss Pk+DG/AuS 15/15/15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zekrom DB+O/FuB 15/15/15</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>719.888888888889</v>
+      </c>
+      <c r="G10">
+        <v>719.888888888889</v>
+      </c>
+      <c r="H10">
+        <v>120</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Zekrom DB+O/FuB 15/15/15</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Charizard (Mega Y) DB+BB/AC 15/15/15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Tyranitar DB+BrS/SE 15/15/15</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>719.4027777777778</v>
+      </c>
+      <c r="G11">
+        <v>719.4027777777778</v>
+      </c>
+      <c r="H11">
+        <v>118</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lineup Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lead Shield</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back Shield</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Best Score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>737.5416666666666</v>
+      </c>
+      <c r="F2">
+        <v>42</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>721.0416666666666</v>
+      </c>
+      <c r="F3">
+        <v>42</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>740.2916666666666</v>
+      </c>
+      <c r="F4">
+        <v>43</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>737.5416666666666</v>
+      </c>
+      <c r="F5">
+        <v>42</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>728.6875</v>
+      </c>
+      <c r="F6">
+        <v>41</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>722.5833333333334</v>
+      </c>
+      <c r="F7">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>737.5416666666666</v>
+      </c>
+      <c r="F8">
+        <v>42</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>709.3333333333334</v>
+      </c>
+      <c r="F9">
+        <v>38</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>736.375</v>
+      </c>
+      <c r="F10">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>728.0208333333334</v>
+      </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>727.3958333333334</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>710.125</v>
+      </c>
+      <c r="F13">
+        <v>41</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>728.0208333333334</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>722.1875</v>
+      </c>
+      <c r="F15">
+        <v>42</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>713.625</v>
+      </c>
+      <c r="F16">
+        <v>39</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>722.2291666666666</v>
+      </c>
+      <c r="F17">
+        <v>39</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>728.7708333333334</v>
+      </c>
+      <c r="F18">
+        <v>41</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>710.5833333333334</v>
+      </c>
+      <c r="F19">
+        <v>40</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>722.2291666666666</v>
+      </c>
+      <c r="F20">
+        <v>39</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>724.5</v>
+      </c>
+      <c r="F21">
+        <v>42</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>714.6875</v>
+      </c>
+      <c r="F22">
+        <v>37</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>722.2291666666666</v>
+      </c>
+      <c r="F23">
+        <v>39</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>705.6458333333334</v>
+      </c>
+      <c r="F24">
+        <v>37</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>732.5833333333334</v>
+      </c>
+      <c r="F25">
+        <v>41</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>726.7083333333334</v>
+      </c>
+      <c r="F26">
+        <v>38</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>729.7708333333334</v>
+      </c>
+      <c r="F27">
+        <v>43</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>703.1875</v>
+      </c>
+      <c r="F28">
+        <v>39</v>
+      </c>
+      <c r="G28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>10</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>728.0208333333334</v>
+      </c>
+      <c r="F29">
+        <v>40</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>694.4375</v>
+      </c>
+      <c r="F30">
+        <v>36</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>735.75</v>
+      </c>
+      <c r="F31">
+        <v>42</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lineups Used</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Lead Lineups Used</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Back Lineups Used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Viable Lineup Rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>All Lineup Rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best Lineup Score</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Message</t>
         </is>
       </c>
     </row>
